--- a/artfynd/A 3062-2025 artfynd.xlsx
+++ b/artfynd/A 3062-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94635450</v>
+        <v>94635383</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>219794</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klaxåsen, Nordanmyren /SV/, fuktstråk, Jmt</t>
+          <t>Klaxåsen, Nordanmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471421.7321650683</v>
+        <v>471501</v>
       </c>
       <c r="R2" t="n">
-        <v>6916466.689821336</v>
+        <v>6916531</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,24 +743,14 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fuktstråk i granskog, mellan dike och skogsbilväg SV om Nordanmyren</t>
+          <t>Nordanmyren. Två mindre kärr i barrskog, det finns ännu fler mot norr. Ordentligt blött i vissa partier, mer framkomligt bitvis.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Fuktig granskog</t>
+          <t>Skogskärr, delvis mycket blöta</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94635451</v>
+        <v>94635403</v>
       </c>
       <c r="B3" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,37 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klaxåsen, Nordanmyren /SV/, fuktstråk, Jmt</t>
+          <t>Klaxåsen, Nordanmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471421.7321650683</v>
+        <v>471501</v>
       </c>
       <c r="R3" t="n">
-        <v>6916466.689821336</v>
+        <v>6916531</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,24 +854,14 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Grunt dike i barrskog i den västra delen av Nordanmyren.</t>
+          <t>Nordanmyren. Två mindre kärr i barrskog, det finns ännu fler mot norr. Ordentligt blött i vissa partier, mer framkomligt bitvis.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Grunt dike i barrskog</t>
+          <t>Skogskärr, delvis mycket blöta</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94635427</v>
+        <v>94635433</v>
       </c>
       <c r="B4" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>220093</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471423.928585708</v>
+        <v>471424</v>
       </c>
       <c r="R4" t="n">
-        <v>6916451.82253033</v>
+        <v>6916452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,19 +965,9 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1053,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94635424</v>
+        <v>94635379</v>
       </c>
       <c r="B5" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,37 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>221063</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klaxåsen, Nordanmyren /SV/, skogskärr, Jmt</t>
+          <t>Klaxåsen, Nordanmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471423.928585708</v>
+        <v>471501</v>
       </c>
       <c r="R5" t="n">
-        <v>6916451.82253033</v>
+        <v>6916531</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,24 +1076,14 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Skogskärr, väster om dike direkt utanför slänt av skogsbilväg SV om Nordanmyren.</t>
+          <t>Nordanmyren. Två mindre kärr i barrskog, det finns ännu fler mot norr. Ordentligt blött i vissa partier, mer framkomligt bitvis.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Litet skogskärr i granskog</t>
+          <t>Skogskärr, delvis mycket blöta</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1179,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94635433</v>
+        <v>94635391</v>
       </c>
       <c r="B6" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,37 +1130,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>221944</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klaxåsen, Nordanmyren /SV/, skogskärr, Jmt</t>
+          <t>Klaxåsen, Nordanmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471423.928585708</v>
+        <v>471501</v>
       </c>
       <c r="R6" t="n">
-        <v>6916451.82253033</v>
+        <v>6916531</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,24 +1183,14 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Skogskärr, väster om dike direkt utanför slänt av skogsbilväg SV om Nordanmyren.</t>
+          <t>Nordanmyren. Två mindre kärr i barrskog, det finns ännu fler mot norr. Ordentligt blött i vissa partier, mer framkomligt bitvis.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,7 +1204,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Litet skogskärr i granskog</t>
+          <t>Skogskärr, delvis mycket blöta</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1298,6 +1219,672 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Atlasinventering och läger i Jämtland</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>94626514</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Klaxåsen, Nordanmyren /S/, skog, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>471539</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6916506</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Skogsmark SV om gård vid Nordanmyren. Barrskog med vindfällda träd och ett par torrakor.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrskog, vindfällen</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Atlasinventering och läger i Jämtland</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>94635424</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Klaxåsen, Nordanmyren /SV/, skogskärr, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>471424</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6916452</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Skogskärr, väster om dike direkt utanför slänt av skogsbilväg SV om Nordanmyren.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Litet skogskärr i granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Atlasinventering och läger i Jämtland</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>94635450</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Klaxåsen, Nordanmyren /SV/, fuktstråk, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>471422</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6916467</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fuktstråk i granskog, mellan dike och skogsbilväg SV om Nordanmyren</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Fuktig granskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Atlasinventering och läger i Jämtland</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>94635397</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100143</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Klaxåsen, Nordanmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>471501</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6916531</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Nordanmyren. Två mindre kärr i barrskog, det finns ännu fler mot norr. Ordentligt blött i vissa partier, mer framkomligt bitvis.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Skogskärr, delvis mycket blöta</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Atlasinventering och läger i Jämtland</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>94635427</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Klaxåsen, Nordanmyren /SV/, skogskärr, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>471424</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6916452</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Skogskärr, väster om dike direkt utanför slänt av skogsbilväg SV om Nordanmyren.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Litet skogskärr i granskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Atlasinventering och läger i Jämtland</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>94635451</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Klaxåsen, Nordanmyren /SV/, fuktstråk, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>471422</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6916467</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Grunt dike i barrskog i den västra delen av Nordanmyren.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grunt dike i barrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Atlasinventering och läger i Jämtland</t>
         </is>

--- a/artfynd/A 3062-2025 artfynd.xlsx
+++ b/artfynd/A 3062-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94635383</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94635403</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94635433</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94635379</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
           <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94635391</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
           <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94626514</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
           <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94635424</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
           <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94635450</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
           <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94635397</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
           <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94635427</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,8 +1944,26 @@
           <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94635451</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>